--- a/docs/planilla-clasificacion-bo-fomento.xlsx
+++ b/docs/planilla-clasificacion-bo-fomento.xlsx
@@ -557,7 +557,7 @@
     <row r="8" ht="30" customHeight="1">
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>En la hoja «Faltan» van los vinos y las milanesas / burgers, que no estaban en las imágenes que recibimos. Se agregan ahí con el mismo formato.</t>
+          <t>En la hoja «Faltan» van las milanesas / burgers y el menú de niños, que no estaban en las cartas que recibimos. Se agregan ahí con el mismo formato.</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W66"/>
+  <dimension ref="A1:W41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -15119,7 +15119,7 @@
       <c r="A2" s="14" t="n"/>
       <c r="B2" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Milanesas y burgers</t>
         </is>
       </c>
       <c r="C2" s="14" t="n"/>
@@ -15148,7 +15148,7 @@
       <c r="A3" s="14" t="n"/>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Milanesas y burgers</t>
         </is>
       </c>
       <c r="C3" s="14" t="n"/>
@@ -15177,7 +15177,7 @@
       <c r="A4" s="14" t="n"/>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Milanesas y burgers</t>
         </is>
       </c>
       <c r="C4" s="14" t="n"/>
@@ -15206,7 +15206,7 @@
       <c r="A5" s="14" t="n"/>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Milanesas y burgers</t>
         </is>
       </c>
       <c r="C5" s="14" t="n"/>
@@ -15235,7 +15235,7 @@
       <c r="A6" s="14" t="n"/>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Milanesas y burgers</t>
         </is>
       </c>
       <c r="C6" s="14" t="n"/>
@@ -15264,7 +15264,7 @@
       <c r="A7" s="14" t="n"/>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Milanesas y burgers</t>
         </is>
       </c>
       <c r="C7" s="14" t="n"/>
@@ -15293,7 +15293,7 @@
       <c r="A8" s="14" t="n"/>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Milanesas y burgers</t>
         </is>
       </c>
       <c r="C8" s="14" t="n"/>
@@ -15322,7 +15322,7 @@
       <c r="A9" s="14" t="n"/>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Milanesas y burgers</t>
         </is>
       </c>
       <c r="C9" s="14" t="n"/>
@@ -15351,7 +15351,7 @@
       <c r="A10" s="14" t="n"/>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Milanesas y burgers</t>
         </is>
       </c>
       <c r="C10" s="14" t="n"/>
@@ -15380,7 +15380,7 @@
       <c r="A11" s="14" t="n"/>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Milanesas y burgers</t>
         </is>
       </c>
       <c r="C11" s="14" t="n"/>
@@ -15409,7 +15409,7 @@
       <c r="A12" s="14" t="n"/>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Milanesas y burgers</t>
         </is>
       </c>
       <c r="C12" s="14" t="n"/>
@@ -15438,7 +15438,7 @@
       <c r="A13" s="14" t="n"/>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Milanesas y burgers</t>
         </is>
       </c>
       <c r="C13" s="14" t="n"/>
@@ -15467,7 +15467,7 @@
       <c r="A14" s="14" t="n"/>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Milanesas y burgers</t>
         </is>
       </c>
       <c r="C14" s="14" t="n"/>
@@ -15496,7 +15496,7 @@
       <c r="A15" s="14" t="n"/>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Milanesas y burgers</t>
         </is>
       </c>
       <c r="C15" s="14" t="n"/>
@@ -15525,7 +15525,7 @@
       <c r="A16" s="14" t="n"/>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Milanesas y burgers</t>
         </is>
       </c>
       <c r="C16" s="14" t="n"/>
@@ -15554,7 +15554,7 @@
       <c r="A17" s="14" t="n"/>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Milanesas y burgers</t>
         </is>
       </c>
       <c r="C17" s="14" t="n"/>
@@ -15583,7 +15583,7 @@
       <c r="A18" s="14" t="n"/>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Milanesas y burgers</t>
         </is>
       </c>
       <c r="C18" s="14" t="n"/>
@@ -15612,7 +15612,7 @@
       <c r="A19" s="14" t="n"/>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Milanesas y burgers</t>
         </is>
       </c>
       <c r="C19" s="14" t="n"/>
@@ -15641,7 +15641,7 @@
       <c r="A20" s="14" t="n"/>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Milanesas y burgers</t>
         </is>
       </c>
       <c r="C20" s="14" t="n"/>
@@ -15670,7 +15670,7 @@
       <c r="A21" s="14" t="n"/>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Milanesas y burgers</t>
         </is>
       </c>
       <c r="C21" s="14" t="n"/>
@@ -15699,7 +15699,7 @@
       <c r="A22" s="14" t="n"/>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Milanesas y burgers</t>
         </is>
       </c>
       <c r="C22" s="14" t="n"/>
@@ -15728,7 +15728,7 @@
       <c r="A23" s="14" t="n"/>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Milanesas y burgers</t>
         </is>
       </c>
       <c r="C23" s="14" t="n"/>
@@ -15757,7 +15757,7 @@
       <c r="A24" s="14" t="n"/>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Milanesas y burgers</t>
         </is>
       </c>
       <c r="C24" s="14" t="n"/>
@@ -15786,7 +15786,7 @@
       <c r="A25" s="14" t="n"/>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Milanesas y burgers</t>
         </is>
       </c>
       <c r="C25" s="14" t="n"/>
@@ -15815,7 +15815,7 @@
       <c r="A26" s="14" t="n"/>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Milanesas y burgers</t>
         </is>
       </c>
       <c r="C26" s="14" t="n"/>
@@ -15844,7 +15844,7 @@
       <c r="A27" s="14" t="n"/>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Menú de niños</t>
         </is>
       </c>
       <c r="C27" s="14" t="n"/>
@@ -15873,7 +15873,7 @@
       <c r="A28" s="14" t="n"/>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Menú de niños</t>
         </is>
       </c>
       <c r="C28" s="14" t="n"/>
@@ -15902,7 +15902,7 @@
       <c r="A29" s="14" t="n"/>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Menú de niños</t>
         </is>
       </c>
       <c r="C29" s="14" t="n"/>
@@ -15931,7 +15931,7 @@
       <c r="A30" s="14" t="n"/>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Menú de niños</t>
         </is>
       </c>
       <c r="C30" s="14" t="n"/>
@@ -15960,7 +15960,7 @@
       <c r="A31" s="14" t="n"/>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Menú de niños</t>
         </is>
       </c>
       <c r="C31" s="14" t="n"/>
@@ -15989,7 +15989,7 @@
       <c r="A32" s="14" t="n"/>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Menú de niños</t>
         </is>
       </c>
       <c r="C32" s="14" t="n"/>
@@ -16018,7 +16018,7 @@
       <c r="A33" s="14" t="n"/>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Menú de niños</t>
         </is>
       </c>
       <c r="C33" s="14" t="n"/>
@@ -16047,7 +16047,7 @@
       <c r="A34" s="14" t="n"/>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Menú de niños</t>
         </is>
       </c>
       <c r="C34" s="14" t="n"/>
@@ -16076,7 +16076,7 @@
       <c r="A35" s="14" t="n"/>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Menú de niños</t>
         </is>
       </c>
       <c r="C35" s="14" t="n"/>
@@ -16105,7 +16105,7 @@
       <c r="A36" s="14" t="n"/>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Menú de niños</t>
         </is>
       </c>
       <c r="C36" s="14" t="n"/>
@@ -16134,7 +16134,7 @@
       <c r="A37" s="14" t="n"/>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Menú de niños</t>
         </is>
       </c>
       <c r="C37" s="14" t="n"/>
@@ -16163,7 +16163,7 @@
       <c r="A38" s="14" t="n"/>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Menú de niños</t>
         </is>
       </c>
       <c r="C38" s="14" t="n"/>
@@ -16192,7 +16192,7 @@
       <c r="A39" s="14" t="n"/>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Menú de niños</t>
         </is>
       </c>
       <c r="C39" s="14" t="n"/>
@@ -16221,7 +16221,7 @@
       <c r="A40" s="14" t="n"/>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Menú de niños</t>
         </is>
       </c>
       <c r="C40" s="14" t="n"/>
@@ -16250,7 +16250,7 @@
       <c r="A41" s="14" t="n"/>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>Vinos</t>
+          <t>Menú de niños</t>
         </is>
       </c>
       <c r="C41" s="14" t="n"/>
@@ -16275,735 +16275,10 @@
       <c r="V41" s="14" t="n"/>
       <c r="W41" s="14" t="n"/>
     </row>
-    <row r="42">
-      <c r="A42" s="14" t="n"/>
-      <c r="B42" s="15" t="inlineStr">
-        <is>
-          <t>Milanesas y burgers</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="n"/>
-      <c r="D42" s="14" t="n"/>
-      <c r="E42" s="14" t="n"/>
-      <c r="F42" s="14" t="n"/>
-      <c r="G42" s="14" t="n"/>
-      <c r="H42" s="14" t="n"/>
-      <c r="I42" s="14" t="n"/>
-      <c r="J42" s="14" t="n"/>
-      <c r="K42" s="14" t="n"/>
-      <c r="L42" s="14" t="n"/>
-      <c r="M42" s="14" t="n"/>
-      <c r="N42" s="14" t="n"/>
-      <c r="O42" s="14" t="n"/>
-      <c r="P42" s="14" t="n"/>
-      <c r="Q42" s="14" t="n"/>
-      <c r="R42" s="14" t="n"/>
-      <c r="S42" s="14" t="n"/>
-      <c r="T42" s="14" t="n"/>
-      <c r="U42" s="14" t="n"/>
-      <c r="V42" s="14" t="n"/>
-      <c r="W42" s="14" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="14" t="n"/>
-      <c r="B43" s="15" t="inlineStr">
-        <is>
-          <t>Milanesas y burgers</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="n"/>
-      <c r="D43" s="14" t="n"/>
-      <c r="E43" s="14" t="n"/>
-      <c r="F43" s="14" t="n"/>
-      <c r="G43" s="14" t="n"/>
-      <c r="H43" s="14" t="n"/>
-      <c r="I43" s="14" t="n"/>
-      <c r="J43" s="14" t="n"/>
-      <c r="K43" s="14" t="n"/>
-      <c r="L43" s="14" t="n"/>
-      <c r="M43" s="14" t="n"/>
-      <c r="N43" s="14" t="n"/>
-      <c r="O43" s="14" t="n"/>
-      <c r="P43" s="14" t="n"/>
-      <c r="Q43" s="14" t="n"/>
-      <c r="R43" s="14" t="n"/>
-      <c r="S43" s="14" t="n"/>
-      <c r="T43" s="14" t="n"/>
-      <c r="U43" s="14" t="n"/>
-      <c r="V43" s="14" t="n"/>
-      <c r="W43" s="14" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="14" t="n"/>
-      <c r="B44" s="15" t="inlineStr">
-        <is>
-          <t>Milanesas y burgers</t>
-        </is>
-      </c>
-      <c r="C44" s="14" t="n"/>
-      <c r="D44" s="14" t="n"/>
-      <c r="E44" s="14" t="n"/>
-      <c r="F44" s="14" t="n"/>
-      <c r="G44" s="14" t="n"/>
-      <c r="H44" s="14" t="n"/>
-      <c r="I44" s="14" t="n"/>
-      <c r="J44" s="14" t="n"/>
-      <c r="K44" s="14" t="n"/>
-      <c r="L44" s="14" t="n"/>
-      <c r="M44" s="14" t="n"/>
-      <c r="N44" s="14" t="n"/>
-      <c r="O44" s="14" t="n"/>
-      <c r="P44" s="14" t="n"/>
-      <c r="Q44" s="14" t="n"/>
-      <c r="R44" s="14" t="n"/>
-      <c r="S44" s="14" t="n"/>
-      <c r="T44" s="14" t="n"/>
-      <c r="U44" s="14" t="n"/>
-      <c r="V44" s="14" t="n"/>
-      <c r="W44" s="14" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="14" t="n"/>
-      <c r="B45" s="15" t="inlineStr">
-        <is>
-          <t>Milanesas y burgers</t>
-        </is>
-      </c>
-      <c r="C45" s="14" t="n"/>
-      <c r="D45" s="14" t="n"/>
-      <c r="E45" s="14" t="n"/>
-      <c r="F45" s="14" t="n"/>
-      <c r="G45" s="14" t="n"/>
-      <c r="H45" s="14" t="n"/>
-      <c r="I45" s="14" t="n"/>
-      <c r="J45" s="14" t="n"/>
-      <c r="K45" s="14" t="n"/>
-      <c r="L45" s="14" t="n"/>
-      <c r="M45" s="14" t="n"/>
-      <c r="N45" s="14" t="n"/>
-      <c r="O45" s="14" t="n"/>
-      <c r="P45" s="14" t="n"/>
-      <c r="Q45" s="14" t="n"/>
-      <c r="R45" s="14" t="n"/>
-      <c r="S45" s="14" t="n"/>
-      <c r="T45" s="14" t="n"/>
-      <c r="U45" s="14" t="n"/>
-      <c r="V45" s="14" t="n"/>
-      <c r="W45" s="14" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="14" t="n"/>
-      <c r="B46" s="15" t="inlineStr">
-        <is>
-          <t>Milanesas y burgers</t>
-        </is>
-      </c>
-      <c r="C46" s="14" t="n"/>
-      <c r="D46" s="14" t="n"/>
-      <c r="E46" s="14" t="n"/>
-      <c r="F46" s="14" t="n"/>
-      <c r="G46" s="14" t="n"/>
-      <c r="H46" s="14" t="n"/>
-      <c r="I46" s="14" t="n"/>
-      <c r="J46" s="14" t="n"/>
-      <c r="K46" s="14" t="n"/>
-      <c r="L46" s="14" t="n"/>
-      <c r="M46" s="14" t="n"/>
-      <c r="N46" s="14" t="n"/>
-      <c r="O46" s="14" t="n"/>
-      <c r="P46" s="14" t="n"/>
-      <c r="Q46" s="14" t="n"/>
-      <c r="R46" s="14" t="n"/>
-      <c r="S46" s="14" t="n"/>
-      <c r="T46" s="14" t="n"/>
-      <c r="U46" s="14" t="n"/>
-      <c r="V46" s="14" t="n"/>
-      <c r="W46" s="14" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="14" t="n"/>
-      <c r="B47" s="15" t="inlineStr">
-        <is>
-          <t>Milanesas y burgers</t>
-        </is>
-      </c>
-      <c r="C47" s="14" t="n"/>
-      <c r="D47" s="14" t="n"/>
-      <c r="E47" s="14" t="n"/>
-      <c r="F47" s="14" t="n"/>
-      <c r="G47" s="14" t="n"/>
-      <c r="H47" s="14" t="n"/>
-      <c r="I47" s="14" t="n"/>
-      <c r="J47" s="14" t="n"/>
-      <c r="K47" s="14" t="n"/>
-      <c r="L47" s="14" t="n"/>
-      <c r="M47" s="14" t="n"/>
-      <c r="N47" s="14" t="n"/>
-      <c r="O47" s="14" t="n"/>
-      <c r="P47" s="14" t="n"/>
-      <c r="Q47" s="14" t="n"/>
-      <c r="R47" s="14" t="n"/>
-      <c r="S47" s="14" t="n"/>
-      <c r="T47" s="14" t="n"/>
-      <c r="U47" s="14" t="n"/>
-      <c r="V47" s="14" t="n"/>
-      <c r="W47" s="14" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="14" t="n"/>
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t>Milanesas y burgers</t>
-        </is>
-      </c>
-      <c r="C48" s="14" t="n"/>
-      <c r="D48" s="14" t="n"/>
-      <c r="E48" s="14" t="n"/>
-      <c r="F48" s="14" t="n"/>
-      <c r="G48" s="14" t="n"/>
-      <c r="H48" s="14" t="n"/>
-      <c r="I48" s="14" t="n"/>
-      <c r="J48" s="14" t="n"/>
-      <c r="K48" s="14" t="n"/>
-      <c r="L48" s="14" t="n"/>
-      <c r="M48" s="14" t="n"/>
-      <c r="N48" s="14" t="n"/>
-      <c r="O48" s="14" t="n"/>
-      <c r="P48" s="14" t="n"/>
-      <c r="Q48" s="14" t="n"/>
-      <c r="R48" s="14" t="n"/>
-      <c r="S48" s="14" t="n"/>
-      <c r="T48" s="14" t="n"/>
-      <c r="U48" s="14" t="n"/>
-      <c r="V48" s="14" t="n"/>
-      <c r="W48" s="14" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="14" t="n"/>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>Milanesas y burgers</t>
-        </is>
-      </c>
-      <c r="C49" s="14" t="n"/>
-      <c r="D49" s="14" t="n"/>
-      <c r="E49" s="14" t="n"/>
-      <c r="F49" s="14" t="n"/>
-      <c r="G49" s="14" t="n"/>
-      <c r="H49" s="14" t="n"/>
-      <c r="I49" s="14" t="n"/>
-      <c r="J49" s="14" t="n"/>
-      <c r="K49" s="14" t="n"/>
-      <c r="L49" s="14" t="n"/>
-      <c r="M49" s="14" t="n"/>
-      <c r="N49" s="14" t="n"/>
-      <c r="O49" s="14" t="n"/>
-      <c r="P49" s="14" t="n"/>
-      <c r="Q49" s="14" t="n"/>
-      <c r="R49" s="14" t="n"/>
-      <c r="S49" s="14" t="n"/>
-      <c r="T49" s="14" t="n"/>
-      <c r="U49" s="14" t="n"/>
-      <c r="V49" s="14" t="n"/>
-      <c r="W49" s="14" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="14" t="n"/>
-      <c r="B50" s="15" t="inlineStr">
-        <is>
-          <t>Milanesas y burgers</t>
-        </is>
-      </c>
-      <c r="C50" s="14" t="n"/>
-      <c r="D50" s="14" t="n"/>
-      <c r="E50" s="14" t="n"/>
-      <c r="F50" s="14" t="n"/>
-      <c r="G50" s="14" t="n"/>
-      <c r="H50" s="14" t="n"/>
-      <c r="I50" s="14" t="n"/>
-      <c r="J50" s="14" t="n"/>
-      <c r="K50" s="14" t="n"/>
-      <c r="L50" s="14" t="n"/>
-      <c r="M50" s="14" t="n"/>
-      <c r="N50" s="14" t="n"/>
-      <c r="O50" s="14" t="n"/>
-      <c r="P50" s="14" t="n"/>
-      <c r="Q50" s="14" t="n"/>
-      <c r="R50" s="14" t="n"/>
-      <c r="S50" s="14" t="n"/>
-      <c r="T50" s="14" t="n"/>
-      <c r="U50" s="14" t="n"/>
-      <c r="V50" s="14" t="n"/>
-      <c r="W50" s="14" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="14" t="n"/>
-      <c r="B51" s="15" t="inlineStr">
-        <is>
-          <t>Milanesas y burgers</t>
-        </is>
-      </c>
-      <c r="C51" s="14" t="n"/>
-      <c r="D51" s="14" t="n"/>
-      <c r="E51" s="14" t="n"/>
-      <c r="F51" s="14" t="n"/>
-      <c r="G51" s="14" t="n"/>
-      <c r="H51" s="14" t="n"/>
-      <c r="I51" s="14" t="n"/>
-      <c r="J51" s="14" t="n"/>
-      <c r="K51" s="14" t="n"/>
-      <c r="L51" s="14" t="n"/>
-      <c r="M51" s="14" t="n"/>
-      <c r="N51" s="14" t="n"/>
-      <c r="O51" s="14" t="n"/>
-      <c r="P51" s="14" t="n"/>
-      <c r="Q51" s="14" t="n"/>
-      <c r="R51" s="14" t="n"/>
-      <c r="S51" s="14" t="n"/>
-      <c r="T51" s="14" t="n"/>
-      <c r="U51" s="14" t="n"/>
-      <c r="V51" s="14" t="n"/>
-      <c r="W51" s="14" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="14" t="n"/>
-      <c r="B52" s="15" t="inlineStr">
-        <is>
-          <t>Milanesas y burgers</t>
-        </is>
-      </c>
-      <c r="C52" s="14" t="n"/>
-      <c r="D52" s="14" t="n"/>
-      <c r="E52" s="14" t="n"/>
-      <c r="F52" s="14" t="n"/>
-      <c r="G52" s="14" t="n"/>
-      <c r="H52" s="14" t="n"/>
-      <c r="I52" s="14" t="n"/>
-      <c r="J52" s="14" t="n"/>
-      <c r="K52" s="14" t="n"/>
-      <c r="L52" s="14" t="n"/>
-      <c r="M52" s="14" t="n"/>
-      <c r="N52" s="14" t="n"/>
-      <c r="O52" s="14" t="n"/>
-      <c r="P52" s="14" t="n"/>
-      <c r="Q52" s="14" t="n"/>
-      <c r="R52" s="14" t="n"/>
-      <c r="S52" s="14" t="n"/>
-      <c r="T52" s="14" t="n"/>
-      <c r="U52" s="14" t="n"/>
-      <c r="V52" s="14" t="n"/>
-      <c r="W52" s="14" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="14" t="n"/>
-      <c r="B53" s="15" t="inlineStr">
-        <is>
-          <t>Milanesas y burgers</t>
-        </is>
-      </c>
-      <c r="C53" s="14" t="n"/>
-      <c r="D53" s="14" t="n"/>
-      <c r="E53" s="14" t="n"/>
-      <c r="F53" s="14" t="n"/>
-      <c r="G53" s="14" t="n"/>
-      <c r="H53" s="14" t="n"/>
-      <c r="I53" s="14" t="n"/>
-      <c r="J53" s="14" t="n"/>
-      <c r="K53" s="14" t="n"/>
-      <c r="L53" s="14" t="n"/>
-      <c r="M53" s="14" t="n"/>
-      <c r="N53" s="14" t="n"/>
-      <c r="O53" s="14" t="n"/>
-      <c r="P53" s="14" t="n"/>
-      <c r="Q53" s="14" t="n"/>
-      <c r="R53" s="14" t="n"/>
-      <c r="S53" s="14" t="n"/>
-      <c r="T53" s="14" t="n"/>
-      <c r="U53" s="14" t="n"/>
-      <c r="V53" s="14" t="n"/>
-      <c r="W53" s="14" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="14" t="n"/>
-      <c r="B54" s="15" t="inlineStr">
-        <is>
-          <t>Milanesas y burgers</t>
-        </is>
-      </c>
-      <c r="C54" s="14" t="n"/>
-      <c r="D54" s="14" t="n"/>
-      <c r="E54" s="14" t="n"/>
-      <c r="F54" s="14" t="n"/>
-      <c r="G54" s="14" t="n"/>
-      <c r="H54" s="14" t="n"/>
-      <c r="I54" s="14" t="n"/>
-      <c r="J54" s="14" t="n"/>
-      <c r="K54" s="14" t="n"/>
-      <c r="L54" s="14" t="n"/>
-      <c r="M54" s="14" t="n"/>
-      <c r="N54" s="14" t="n"/>
-      <c r="O54" s="14" t="n"/>
-      <c r="P54" s="14" t="n"/>
-      <c r="Q54" s="14" t="n"/>
-      <c r="R54" s="14" t="n"/>
-      <c r="S54" s="14" t="n"/>
-      <c r="T54" s="14" t="n"/>
-      <c r="U54" s="14" t="n"/>
-      <c r="V54" s="14" t="n"/>
-      <c r="W54" s="14" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="14" t="n"/>
-      <c r="B55" s="15" t="inlineStr">
-        <is>
-          <t>Milanesas y burgers</t>
-        </is>
-      </c>
-      <c r="C55" s="14" t="n"/>
-      <c r="D55" s="14" t="n"/>
-      <c r="E55" s="14" t="n"/>
-      <c r="F55" s="14" t="n"/>
-      <c r="G55" s="14" t="n"/>
-      <c r="H55" s="14" t="n"/>
-      <c r="I55" s="14" t="n"/>
-      <c r="J55" s="14" t="n"/>
-      <c r="K55" s="14" t="n"/>
-      <c r="L55" s="14" t="n"/>
-      <c r="M55" s="14" t="n"/>
-      <c r="N55" s="14" t="n"/>
-      <c r="O55" s="14" t="n"/>
-      <c r="P55" s="14" t="n"/>
-      <c r="Q55" s="14" t="n"/>
-      <c r="R55" s="14" t="n"/>
-      <c r="S55" s="14" t="n"/>
-      <c r="T55" s="14" t="n"/>
-      <c r="U55" s="14" t="n"/>
-      <c r="V55" s="14" t="n"/>
-      <c r="W55" s="14" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="14" t="n"/>
-      <c r="B56" s="15" t="inlineStr">
-        <is>
-          <t>Milanesas y burgers</t>
-        </is>
-      </c>
-      <c r="C56" s="14" t="n"/>
-      <c r="D56" s="14" t="n"/>
-      <c r="E56" s="14" t="n"/>
-      <c r="F56" s="14" t="n"/>
-      <c r="G56" s="14" t="n"/>
-      <c r="H56" s="14" t="n"/>
-      <c r="I56" s="14" t="n"/>
-      <c r="J56" s="14" t="n"/>
-      <c r="K56" s="14" t="n"/>
-      <c r="L56" s="14" t="n"/>
-      <c r="M56" s="14" t="n"/>
-      <c r="N56" s="14" t="n"/>
-      <c r="O56" s="14" t="n"/>
-      <c r="P56" s="14" t="n"/>
-      <c r="Q56" s="14" t="n"/>
-      <c r="R56" s="14" t="n"/>
-      <c r="S56" s="14" t="n"/>
-      <c r="T56" s="14" t="n"/>
-      <c r="U56" s="14" t="n"/>
-      <c r="V56" s="14" t="n"/>
-      <c r="W56" s="14" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="14" t="n"/>
-      <c r="B57" s="15" t="inlineStr">
-        <is>
-          <t>Milanesas y burgers</t>
-        </is>
-      </c>
-      <c r="C57" s="14" t="n"/>
-      <c r="D57" s="14" t="n"/>
-      <c r="E57" s="14" t="n"/>
-      <c r="F57" s="14" t="n"/>
-      <c r="G57" s="14" t="n"/>
-      <c r="H57" s="14" t="n"/>
-      <c r="I57" s="14" t="n"/>
-      <c r="J57" s="14" t="n"/>
-      <c r="K57" s="14" t="n"/>
-      <c r="L57" s="14" t="n"/>
-      <c r="M57" s="14" t="n"/>
-      <c r="N57" s="14" t="n"/>
-      <c r="O57" s="14" t="n"/>
-      <c r="P57" s="14" t="n"/>
-      <c r="Q57" s="14" t="n"/>
-      <c r="R57" s="14" t="n"/>
-      <c r="S57" s="14" t="n"/>
-      <c r="T57" s="14" t="n"/>
-      <c r="U57" s="14" t="n"/>
-      <c r="V57" s="14" t="n"/>
-      <c r="W57" s="14" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="14" t="n"/>
-      <c r="B58" s="15" t="inlineStr">
-        <is>
-          <t>Milanesas y burgers</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="n"/>
-      <c r="D58" s="14" t="n"/>
-      <c r="E58" s="14" t="n"/>
-      <c r="F58" s="14" t="n"/>
-      <c r="G58" s="14" t="n"/>
-      <c r="H58" s="14" t="n"/>
-      <c r="I58" s="14" t="n"/>
-      <c r="J58" s="14" t="n"/>
-      <c r="K58" s="14" t="n"/>
-      <c r="L58" s="14" t="n"/>
-      <c r="M58" s="14" t="n"/>
-      <c r="N58" s="14" t="n"/>
-      <c r="O58" s="14" t="n"/>
-      <c r="P58" s="14" t="n"/>
-      <c r="Q58" s="14" t="n"/>
-      <c r="R58" s="14" t="n"/>
-      <c r="S58" s="14" t="n"/>
-      <c r="T58" s="14" t="n"/>
-      <c r="U58" s="14" t="n"/>
-      <c r="V58" s="14" t="n"/>
-      <c r="W58" s="14" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="14" t="n"/>
-      <c r="B59" s="15" t="inlineStr">
-        <is>
-          <t>Milanesas y burgers</t>
-        </is>
-      </c>
-      <c r="C59" s="14" t="n"/>
-      <c r="D59" s="14" t="n"/>
-      <c r="E59" s="14" t="n"/>
-      <c r="F59" s="14" t="n"/>
-      <c r="G59" s="14" t="n"/>
-      <c r="H59" s="14" t="n"/>
-      <c r="I59" s="14" t="n"/>
-      <c r="J59" s="14" t="n"/>
-      <c r="K59" s="14" t="n"/>
-      <c r="L59" s="14" t="n"/>
-      <c r="M59" s="14" t="n"/>
-      <c r="N59" s="14" t="n"/>
-      <c r="O59" s="14" t="n"/>
-      <c r="P59" s="14" t="n"/>
-      <c r="Q59" s="14" t="n"/>
-      <c r="R59" s="14" t="n"/>
-      <c r="S59" s="14" t="n"/>
-      <c r="T59" s="14" t="n"/>
-      <c r="U59" s="14" t="n"/>
-      <c r="V59" s="14" t="n"/>
-      <c r="W59" s="14" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="14" t="n"/>
-      <c r="B60" s="15" t="inlineStr">
-        <is>
-          <t>Milanesas y burgers</t>
-        </is>
-      </c>
-      <c r="C60" s="14" t="n"/>
-      <c r="D60" s="14" t="n"/>
-      <c r="E60" s="14" t="n"/>
-      <c r="F60" s="14" t="n"/>
-      <c r="G60" s="14" t="n"/>
-      <c r="H60" s="14" t="n"/>
-      <c r="I60" s="14" t="n"/>
-      <c r="J60" s="14" t="n"/>
-      <c r="K60" s="14" t="n"/>
-      <c r="L60" s="14" t="n"/>
-      <c r="M60" s="14" t="n"/>
-      <c r="N60" s="14" t="n"/>
-      <c r="O60" s="14" t="n"/>
-      <c r="P60" s="14" t="n"/>
-      <c r="Q60" s="14" t="n"/>
-      <c r="R60" s="14" t="n"/>
-      <c r="S60" s="14" t="n"/>
-      <c r="T60" s="14" t="n"/>
-      <c r="U60" s="14" t="n"/>
-      <c r="V60" s="14" t="n"/>
-      <c r="W60" s="14" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="14" t="n"/>
-      <c r="B61" s="15" t="inlineStr">
-        <is>
-          <t>Milanesas y burgers</t>
-        </is>
-      </c>
-      <c r="C61" s="14" t="n"/>
-      <c r="D61" s="14" t="n"/>
-      <c r="E61" s="14" t="n"/>
-      <c r="F61" s="14" t="n"/>
-      <c r="G61" s="14" t="n"/>
-      <c r="H61" s="14" t="n"/>
-      <c r="I61" s="14" t="n"/>
-      <c r="J61" s="14" t="n"/>
-      <c r="K61" s="14" t="n"/>
-      <c r="L61" s="14" t="n"/>
-      <c r="M61" s="14" t="n"/>
-      <c r="N61" s="14" t="n"/>
-      <c r="O61" s="14" t="n"/>
-      <c r="P61" s="14" t="n"/>
-      <c r="Q61" s="14" t="n"/>
-      <c r="R61" s="14" t="n"/>
-      <c r="S61" s="14" t="n"/>
-      <c r="T61" s="14" t="n"/>
-      <c r="U61" s="14" t="n"/>
-      <c r="V61" s="14" t="n"/>
-      <c r="W61" s="14" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="14" t="n"/>
-      <c r="B62" s="15" t="inlineStr">
-        <is>
-          <t>Milanesas y burgers</t>
-        </is>
-      </c>
-      <c r="C62" s="14" t="n"/>
-      <c r="D62" s="14" t="n"/>
-      <c r="E62" s="14" t="n"/>
-      <c r="F62" s="14" t="n"/>
-      <c r="G62" s="14" t="n"/>
-      <c r="H62" s="14" t="n"/>
-      <c r="I62" s="14" t="n"/>
-      <c r="J62" s="14" t="n"/>
-      <c r="K62" s="14" t="n"/>
-      <c r="L62" s="14" t="n"/>
-      <c r="M62" s="14" t="n"/>
-      <c r="N62" s="14" t="n"/>
-      <c r="O62" s="14" t="n"/>
-      <c r="P62" s="14" t="n"/>
-      <c r="Q62" s="14" t="n"/>
-      <c r="R62" s="14" t="n"/>
-      <c r="S62" s="14" t="n"/>
-      <c r="T62" s="14" t="n"/>
-      <c r="U62" s="14" t="n"/>
-      <c r="V62" s="14" t="n"/>
-      <c r="W62" s="14" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="14" t="n"/>
-      <c r="B63" s="15" t="inlineStr">
-        <is>
-          <t>Milanesas y burgers</t>
-        </is>
-      </c>
-      <c r="C63" s="14" t="n"/>
-      <c r="D63" s="14" t="n"/>
-      <c r="E63" s="14" t="n"/>
-      <c r="F63" s="14" t="n"/>
-      <c r="G63" s="14" t="n"/>
-      <c r="H63" s="14" t="n"/>
-      <c r="I63" s="14" t="n"/>
-      <c r="J63" s="14" t="n"/>
-      <c r="K63" s="14" t="n"/>
-      <c r="L63" s="14" t="n"/>
-      <c r="M63" s="14" t="n"/>
-      <c r="N63" s="14" t="n"/>
-      <c r="O63" s="14" t="n"/>
-      <c r="P63" s="14" t="n"/>
-      <c r="Q63" s="14" t="n"/>
-      <c r="R63" s="14" t="n"/>
-      <c r="S63" s="14" t="n"/>
-      <c r="T63" s="14" t="n"/>
-      <c r="U63" s="14" t="n"/>
-      <c r="V63" s="14" t="n"/>
-      <c r="W63" s="14" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="14" t="n"/>
-      <c r="B64" s="15" t="inlineStr">
-        <is>
-          <t>Milanesas y burgers</t>
-        </is>
-      </c>
-      <c r="C64" s="14" t="n"/>
-      <c r="D64" s="14" t="n"/>
-      <c r="E64" s="14" t="n"/>
-      <c r="F64" s="14" t="n"/>
-      <c r="G64" s="14" t="n"/>
-      <c r="H64" s="14" t="n"/>
-      <c r="I64" s="14" t="n"/>
-      <c r="J64" s="14" t="n"/>
-      <c r="K64" s="14" t="n"/>
-      <c r="L64" s="14" t="n"/>
-      <c r="M64" s="14" t="n"/>
-      <c r="N64" s="14" t="n"/>
-      <c r="O64" s="14" t="n"/>
-      <c r="P64" s="14" t="n"/>
-      <c r="Q64" s="14" t="n"/>
-      <c r="R64" s="14" t="n"/>
-      <c r="S64" s="14" t="n"/>
-      <c r="T64" s="14" t="n"/>
-      <c r="U64" s="14" t="n"/>
-      <c r="V64" s="14" t="n"/>
-      <c r="W64" s="14" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="14" t="n"/>
-      <c r="B65" s="15" t="inlineStr">
-        <is>
-          <t>Milanesas y burgers</t>
-        </is>
-      </c>
-      <c r="C65" s="14" t="n"/>
-      <c r="D65" s="14" t="n"/>
-      <c r="E65" s="14" t="n"/>
-      <c r="F65" s="14" t="n"/>
-      <c r="G65" s="14" t="n"/>
-      <c r="H65" s="14" t="n"/>
-      <c r="I65" s="14" t="n"/>
-      <c r="J65" s="14" t="n"/>
-      <c r="K65" s="14" t="n"/>
-      <c r="L65" s="14" t="n"/>
-      <c r="M65" s="14" t="n"/>
-      <c r="N65" s="14" t="n"/>
-      <c r="O65" s="14" t="n"/>
-      <c r="P65" s="14" t="n"/>
-      <c r="Q65" s="14" t="n"/>
-      <c r="R65" s="14" t="n"/>
-      <c r="S65" s="14" t="n"/>
-      <c r="T65" s="14" t="n"/>
-      <c r="U65" s="14" t="n"/>
-      <c r="V65" s="14" t="n"/>
-      <c r="W65" s="14" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="14" t="n"/>
-      <c r="B66" s="15" t="inlineStr">
-        <is>
-          <t>Milanesas y burgers</t>
-        </is>
-      </c>
-      <c r="C66" s="14" t="n"/>
-      <c r="D66" s="14" t="n"/>
-      <c r="E66" s="14" t="n"/>
-      <c r="F66" s="14" t="n"/>
-      <c r="G66" s="14" t="n"/>
-      <c r="H66" s="14" t="n"/>
-      <c r="I66" s="14" t="n"/>
-      <c r="J66" s="14" t="n"/>
-      <c r="K66" s="14" t="n"/>
-      <c r="L66" s="14" t="n"/>
-      <c r="M66" s="14" t="n"/>
-      <c r="N66" s="14" t="n"/>
-      <c r="O66" s="14" t="n"/>
-      <c r="P66" s="14" t="n"/>
-      <c r="Q66" s="14" t="n"/>
-      <c r="R66" s="14" t="n"/>
-      <c r="S66" s="14" t="n"/>
-      <c r="T66" s="14" t="n"/>
-      <c r="U66" s="14" t="n"/>
-      <c r="V66" s="14" t="n"/>
-      <c r="W66" s="14" t="n"/>
-    </row>
   </sheetData>
   <autoFilter ref="A1:W1"/>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F67 H2:H67 I2:I67 J2:J67 K2:K67 L2:L67 M2:M67 N2:N67 O2:O67 P2:P67 Q2:Q67 R2:R67 S2:S67 T2:T67 U2:U67 V2:V67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Poné sí o no." type="list">
+    <dataValidation sqref="F2:F42 H2:H42 I2:I42 J2:J42 K2:K42 L2:L42 M2:M42 N2:N42 O2:O42 P2:P42 Q2:Q42 R2:R42 S2:S42 T2:T42 U2:U42 V2:V42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Poné sí o no." type="list">
       <formula1>"sí,no"</formula1>
     </dataValidation>
   </dataValidations>
